--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-12).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-12).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 9.138,36</t>
-  </si>
-  <si>
-    <t>96.7</t>
-  </si>
-  <si>
-    <t>61.0</t>
-  </si>
-  <si>
-    <t>5.92</t>
-  </si>
-  <si>
-    <t>19.8</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 9.149,02</t>
+  </si>
+  <si>
+    <t>96.9</t>
+  </si>
+  <si>
+    <t>60.8</t>
+  </si>
+  <si>
+    <t>5.91</t>
+  </si>
+  <si>
+    <t>19.7</t>
   </si>
   <si>
     <t>7.1</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>34.9%</t>
-  </si>
-  <si>
-    <t>16.5%</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>35.0%</t>
+  </si>
+  <si>
+    <t>16.4%</t>
   </si>
   <si>
     <t>1.7%</t>
@@ -989,10 +989,10 @@
     <t>4.4%</t>
   </si>
   <si>
-    <t>2269.0</t>
-  </si>
-  <si>
-    <t>1863.0</t>
+    <t>2270.0</t>
+  </si>
+  <si>
+    <t>1864.0</t>
   </si>
   <si>
     <t>192.0</t>
@@ -1010,7 +1010,7 @@
     <t>15.0</t>
   </si>
   <si>
-    <t>700.0</t>
+    <t>701.0</t>
   </si>
   <si>
     <t>264.0</t>
@@ -10111,7 +10111,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10141,18 +10141,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>11133.440000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <v>125</v>
+      </c>
       <c r="O58" s="6">
         <v>97</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>3.5377952755905513</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>16.395659375000001</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.3771474226804123</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.40625</v>
+      </c>
       <c r="U58" s="9">
         <v>0.1134020618556701</v>
       </c>
@@ -18006,7 +18018,9 @@
       <c r="N111" s="6">
         <v>19</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>17</v>
+      </c>
       <c r="P111" s="7">
         <v>4.1078947368421055</v>
       </c>
@@ -18016,31 +18030,75 @@
       <c r="R111" s="8">
         <v>2.8539235294117646</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.70588235294117652</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -28258,7 +28316,9 @@
       <c r="N179" s="6">
         <v>132</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>70</v>
+      </c>
       <c r="P179" s="7">
         <v>4.4082053846153846</v>
       </c>
@@ -28268,31 +28328,75 @@
       <c r="R179" s="8">
         <v>1.8164285714285715</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.7857142857142857</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
